--- a/podaci/Golovi Leto 2026.xlsx
+++ b/podaci/Golovi Leto 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\beoog\Desktop\Fudbal Bezanija\FK_Baranda_sajt\podaci\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7DD0195-63F9-4126-8947-61AC2A86E995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF69CE51-9850-4604-84BC-3B428652132D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Golovi" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="40">
   <si>
     <t>No.</t>
   </si>
@@ -859,23 +859,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N591"/>
-  <sheetFormatPr defaultColWidth="19.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="19.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.44140625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="7.44140625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.5546875" style="1"/>
-    <col min="14" max="14" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="7.42578125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.5703125" style="1"/>
+    <col min="14" max="14" width="23.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="22.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="22.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -910,7 +910,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="15">
         <v>1</v>
       </c>
@@ -946,7 +946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="14">
         <v>1</v>
       </c>
@@ -984,7 +984,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="14">
         <v>1</v>
       </c>
@@ -1022,7 +1022,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="14">
         <v>1</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="14">
         <v>1</v>
       </c>
@@ -1098,7 +1098,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="14">
         <v>1</v>
       </c>
@@ -1136,7 +1136,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="14">
         <v>1</v>
       </c>
@@ -1174,7 +1174,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="14">
         <v>1</v>
       </c>
@@ -1212,7 +1212,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="14">
         <v>1</v>
       </c>
@@ -1250,7 +1250,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="14">
         <v>1</v>
       </c>
@@ -1288,7 +1288,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="14">
         <v>1</v>
       </c>
@@ -1326,7 +1326,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="14">
         <v>1</v>
       </c>
@@ -1364,7 +1364,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="14">
         <v>1</v>
       </c>
@@ -1402,7 +1402,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="14">
         <v>1</v>
       </c>
@@ -1440,7 +1440,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="14">
         <v>2</v>
       </c>
@@ -1476,7 +1476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="14">
         <v>2</v>
       </c>
@@ -1514,7 +1514,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="14">
         <v>2</v>
       </c>
@@ -1552,7 +1552,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="14">
         <v>2</v>
       </c>
@@ -1590,7 +1590,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="14">
         <v>2</v>
       </c>
@@ -1628,7 +1628,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="14">
         <v>2</v>
       </c>
@@ -1666,7 +1666,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="14">
         <v>2</v>
       </c>
@@ -1704,7 +1704,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="14">
         <v>2</v>
       </c>
@@ -1742,7 +1742,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="14">
         <v>2</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="14">
         <v>2</v>
       </c>
@@ -1818,7 +1818,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="14">
         <v>2</v>
       </c>
@@ -1856,7 +1856,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="14">
         <v>3</v>
       </c>
@@ -1892,7 +1892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="14">
         <v>3</v>
       </c>
@@ -1930,7 +1930,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="14">
         <v>3</v>
       </c>
@@ -1968,7 +1968,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="14">
         <v>3</v>
       </c>
@@ -2006,7 +2006,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="14">
         <v>3</v>
       </c>
@@ -2044,7 +2044,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="14">
         <v>3</v>
       </c>
@@ -2082,7 +2082,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="14">
         <v>3</v>
       </c>
@@ -2120,7 +2120,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="14">
         <v>3</v>
       </c>
@@ -2158,7 +2158,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="14">
         <v>3</v>
       </c>
@@ -2196,7 +2196,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="14">
         <v>3</v>
       </c>
@@ -2234,7 +2234,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="14">
         <v>3</v>
       </c>
@@ -2272,7 +2272,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="14">
         <v>3</v>
       </c>
@@ -2310,7 +2310,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="14">
         <v>3</v>
       </c>
@@ -2348,7 +2348,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="14">
         <v>4</v>
       </c>
@@ -2384,7 +2384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="14">
         <v>4</v>
       </c>
@@ -2422,7 +2422,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="14">
         <v>4</v>
       </c>
@@ -2460,7 +2460,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="14">
         <v>4</v>
       </c>
@@ -2498,7 +2498,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="14">
         <v>4</v>
       </c>
@@ -2536,7 +2536,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="14">
         <v>4</v>
       </c>
@@ -2574,7 +2574,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="14">
         <v>4</v>
       </c>
@@ -2612,7 +2612,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="14">
         <v>4</v>
       </c>
@@ -2650,7 +2650,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="14">
         <v>4</v>
       </c>
@@ -2688,7 +2688,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="14">
         <v>4</v>
       </c>
@@ -2726,7 +2726,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="14">
         <v>4</v>
       </c>
@@ -2764,7 +2764,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="14">
         <v>4</v>
       </c>
@@ -2802,7 +2802,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="14">
         <v>4</v>
       </c>
@@ -2840,7 +2840,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="14">
         <v>4</v>
       </c>
@@ -2878,7 +2878,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="14">
         <v>4</v>
       </c>
@@ -2916,7 +2916,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="14">
         <v>4</v>
       </c>
@@ -2954,7 +2954,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="14">
         <v>4</v>
       </c>
@@ -2992,7 +2992,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="14">
         <v>4</v>
       </c>
@@ -3030,7 +3030,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="14">
         <v>4</v>
       </c>
@@ -3068,7 +3068,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="14">
         <v>4</v>
       </c>
@@ -3106,7 +3106,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="14">
         <v>4</v>
       </c>
@@ -3144,7 +3144,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="14">
         <v>4</v>
       </c>
@@ -3182,7 +3182,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="14">
         <v>4</v>
       </c>
@@ -3220,7 +3220,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="14">
         <v>5</v>
       </c>
@@ -3256,7 +3256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="14">
         <v>5</v>
       </c>
@@ -3294,7 +3294,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="14">
         <v>5</v>
       </c>
@@ -3332,7 +3332,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="14">
         <v>5</v>
       </c>
@@ -3370,7 +3370,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="14">
         <v>5</v>
       </c>
@@ -3408,7 +3408,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="14">
         <v>5</v>
       </c>
@@ -3446,7 +3446,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="14">
         <v>5</v>
       </c>
@@ -3484,7 +3484,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="14">
         <v>5</v>
       </c>
@@ -3522,7 +3522,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="14">
         <v>5</v>
       </c>
@@ -3560,7 +3560,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="14">
         <v>5</v>
       </c>
@@ -3598,7 +3598,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="14">
         <v>5</v>
       </c>
@@ -3636,7 +3636,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="14">
         <v>5</v>
       </c>
@@ -3674,7 +3674,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="14">
         <v>5</v>
       </c>
@@ -3712,7 +3712,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="14">
         <v>5</v>
       </c>
@@ -3750,7 +3750,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="14">
         <v>5</v>
       </c>
@@ -3788,7 +3788,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="14">
         <v>5</v>
       </c>
@@ -3826,7 +3826,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="14">
         <v>6</v>
       </c>
@@ -3862,7 +3862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="14">
         <v>6</v>
       </c>
@@ -3900,7 +3900,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="14">
         <v>6</v>
       </c>
@@ -3938,7 +3938,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="14">
         <v>6</v>
       </c>
@@ -3976,7 +3976,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="14">
         <v>6</v>
       </c>
@@ -4014,7 +4014,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="14">
         <v>6</v>
       </c>
@@ -4052,7 +4052,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="14">
         <v>6</v>
       </c>
@@ -4090,7 +4090,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="14">
         <v>6</v>
       </c>
@@ -4128,7 +4128,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="14">
         <v>6</v>
       </c>
@@ -4166,7 +4166,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="14">
         <v>6</v>
       </c>
@@ -4204,7 +4204,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="14">
         <v>6</v>
       </c>
@@ -4242,7 +4242,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="14">
         <v>6</v>
       </c>
@@ -4280,7 +4280,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="14">
         <v>6</v>
       </c>
@@ -4318,7 +4318,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="14">
         <v>6</v>
       </c>
@@ -4356,7 +4356,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="14">
         <v>6</v>
       </c>
@@ -4394,7 +4394,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="14">
         <v>6</v>
       </c>
@@ -4432,7 +4432,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" s="14">
         <v>6</v>
       </c>
@@ -4470,7 +4470,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="14">
         <v>6</v>
       </c>
@@ -4508,7 +4508,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="14">
         <v>6</v>
       </c>
@@ -4546,7 +4546,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="14">
         <v>6</v>
       </c>
@@ -4584,7 +4584,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="14">
         <v>7</v>
       </c>
@@ -4620,7 +4620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="14">
         <v>7</v>
       </c>
@@ -4658,7 +4658,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="14">
         <v>7</v>
       </c>
@@ -4696,7 +4696,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="14">
         <v>7</v>
       </c>
@@ -4734,7 +4734,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="14">
         <v>7</v>
       </c>
@@ -4772,7 +4772,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" s="14">
         <v>7</v>
       </c>
@@ -4810,7 +4810,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="14">
         <v>7</v>
       </c>
@@ -4848,7 +4848,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="14">
         <v>7</v>
       </c>
@@ -4886,7 +4886,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" s="14">
         <v>7</v>
       </c>
@@ -4924,7 +4924,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" s="14">
         <v>7</v>
       </c>
@@ -4962,7 +4962,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" s="14">
         <v>7</v>
       </c>
@@ -5000,7 +5000,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" s="14">
         <v>7</v>
       </c>
@@ -5038,7 +5038,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" s="14">
         <v>7</v>
       </c>
@@ -5076,7 +5076,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="14">
         <v>7</v>
       </c>
@@ -5114,7 +5114,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" s="14">
         <v>7</v>
       </c>
@@ -5152,7 +5152,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" s="14">
         <v>7</v>
       </c>
@@ -5190,7 +5190,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" s="14">
         <v>7</v>
       </c>
@@ -5228,7 +5228,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" s="14">
         <v>7</v>
       </c>
@@ -5266,7 +5266,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" s="14">
         <v>7</v>
       </c>
@@ -5304,7 +5304,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" s="14">
         <v>7</v>
       </c>
@@ -5342,7 +5342,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" s="14">
         <v>7</v>
       </c>
@@ -5380,7 +5380,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" s="14">
         <v>7</v>
       </c>
@@ -5418,7 +5418,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" s="14">
         <v>7</v>
       </c>
@@ -5456,7 +5456,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" s="14">
         <v>7</v>
       </c>
@@ -5494,7 +5494,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" s="14">
         <v>7</v>
       </c>
@@ -5532,7 +5532,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" s="14">
         <v>7</v>
       </c>
@@ -5570,7 +5570,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" s="14">
         <v>7</v>
       </c>
@@ -5608,7 +5608,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" s="14">
         <v>7</v>
       </c>
@@ -5646,7 +5646,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" s="14">
         <v>7</v>
       </c>
@@ -5684,7 +5684,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" s="14">
         <v>7</v>
       </c>
@@ -5722,7 +5722,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A129" s="14">
         <v>7</v>
       </c>
@@ -5760,7 +5760,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A130" s="14">
         <v>7</v>
       </c>
@@ -5798,593 +5798,1013 @@
         <v>32</v>
       </c>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A131" s="14"/>
-      <c r="B131" s="12"/>
-      <c r="C131" s="2"/>
-      <c r="D131" s="18"/>
-      <c r="E131" s="24"/>
-      <c r="F131" s="18"/>
-      <c r="G131" s="2"/>
-      <c r="H131" s="2"/>
-      <c r="I131" s="2"/>
-      <c r="J131" s="2"/>
+    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A131" s="14">
+        <v>8</v>
+      </c>
+      <c r="B131" s="12">
+        <v>20260831</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D131" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E131" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="F131" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G131" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H131" s="2">
+        <v>1</v>
+      </c>
+      <c r="I131" s="2">
+        <v>1</v>
+      </c>
+      <c r="J131" s="2">
+        <v>0</v>
+      </c>
       <c r="K131" s="4">
         <f t="shared" ref="K131:K194" si="6">I131+J131</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M131" s="1"/>
       <c r="N131" s="1"/>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A132" s="14"/>
-      <c r="B132" s="12"/>
-      <c r="C132" s="2"/>
-      <c r="D132" s="18"/>
-      <c r="E132" s="24"/>
-      <c r="F132" s="18"/>
-      <c r="G132" s="2"/>
-      <c r="H132" s="2"/>
+    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A132" s="14">
+        <v>8</v>
+      </c>
+      <c r="B132" s="12">
+        <v>20260831</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D132" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E132" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="F132" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="G132" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H132" s="2">
+        <v>7</v>
+      </c>
       <c r="I132" s="2">
         <f t="shared" ref="I132:I160" si="7">IF(C132="Black", I131+1,I131)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J132" s="2">
         <f t="shared" ref="J132:J160" si="8">IF(C132="White", J131+1,J131)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K132" s="4">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M132" s="1"/>
       <c r="N132" s="1"/>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A133" s="14"/>
-      <c r="B133" s="12"/>
-      <c r="C133" s="2"/>
-      <c r="D133" s="18"/>
-      <c r="E133" s="24"/>
-      <c r="F133" s="18"/>
-      <c r="G133" s="2"/>
-      <c r="H133" s="2"/>
+    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A133" s="14">
+        <v>8</v>
+      </c>
+      <c r="B133" s="12">
+        <v>20260831</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D133" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="E133" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="F133" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G133" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H133" s="2">
+        <v>11</v>
+      </c>
       <c r="I133" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J133" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K133" s="4">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M133" s="1"/>
       <c r="N133" s="1"/>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A134" s="14"/>
-      <c r="B134" s="12"/>
-      <c r="C134" s="2"/>
-      <c r="D134" s="18"/>
-      <c r="E134" s="24"/>
-      <c r="F134" s="18"/>
-      <c r="G134" s="2"/>
-      <c r="H134" s="2"/>
+    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A134" s="14">
+        <v>8</v>
+      </c>
+      <c r="B134" s="12">
+        <v>20260831</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D134" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E134" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="F134" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="G134" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H134" s="2">
+        <v>12</v>
+      </c>
       <c r="I134" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J134" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K134" s="4">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M134" s="1"/>
       <c r="N134" s="1"/>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A135" s="14"/>
-      <c r="B135" s="12"/>
-      <c r="C135" s="2"/>
-      <c r="D135" s="18"/>
-      <c r="E135" s="24"/>
-      <c r="F135" s="18"/>
-      <c r="G135" s="2"/>
-      <c r="H135" s="2"/>
+    <row r="135" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A135" s="14">
+        <v>8</v>
+      </c>
+      <c r="B135" s="12">
+        <v>20260831</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D135" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E135" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="F135" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="G135" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H135" s="2">
+        <v>13</v>
+      </c>
       <c r="I135" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J135" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K135" s="4">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M135" s="1"/>
       <c r="N135" s="1"/>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A136" s="14"/>
-      <c r="B136" s="12"/>
-      <c r="C136" s="2"/>
-      <c r="D136" s="18"/>
-      <c r="E136" s="24"/>
-      <c r="F136" s="18"/>
-      <c r="G136" s="2"/>
-      <c r="H136" s="2"/>
+    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A136" s="14">
+        <v>8</v>
+      </c>
+      <c r="B136" s="12">
+        <v>20260831</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D136" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="E136" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="F136" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="G136" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H136" s="2">
+        <v>15</v>
+      </c>
       <c r="I136" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J136" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K136" s="4">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M136" s="1"/>
       <c r="N136" s="1"/>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A137" s="14"/>
-      <c r="B137" s="12"/>
-      <c r="C137" s="2"/>
-      <c r="D137" s="18"/>
-      <c r="E137" s="24"/>
-      <c r="F137" s="18"/>
-      <c r="G137" s="2"/>
-      <c r="H137" s="2"/>
+    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A137" s="14">
+        <v>8</v>
+      </c>
+      <c r="B137" s="12">
+        <v>20260831</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D137" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E137" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="F137" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="G137" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H137" s="2">
+        <v>16</v>
+      </c>
       <c r="I137" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J137" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K137" s="4">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M137" s="1"/>
       <c r="N137" s="1"/>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A138" s="14"/>
-      <c r="B138" s="12"/>
-      <c r="C138" s="2"/>
-      <c r="D138" s="18"/>
-      <c r="E138" s="24"/>
-      <c r="F138" s="18"/>
-      <c r="G138" s="2"/>
-      <c r="H138" s="2"/>
+    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A138" s="14">
+        <v>8</v>
+      </c>
+      <c r="B138" s="12">
+        <v>20260831</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D138" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="E138" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="F138" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G138" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H138" s="2">
+        <v>17</v>
+      </c>
       <c r="I138" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J138" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K138" s="4">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M138" s="1"/>
       <c r="N138" s="1"/>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A139" s="14"/>
-      <c r="B139" s="12"/>
-      <c r="C139" s="2"/>
-      <c r="D139" s="18"/>
-      <c r="E139" s="24"/>
-      <c r="F139" s="18"/>
-      <c r="G139" s="2"/>
-      <c r="H139" s="2"/>
+    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A139" s="14">
+        <v>8</v>
+      </c>
+      <c r="B139" s="12">
+        <v>20260831</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D139" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="E139" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="F139" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G139" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H139" s="2">
+        <v>24</v>
+      </c>
       <c r="I139" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J139" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K139" s="4">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M139" s="1"/>
       <c r="N139" s="1"/>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A140" s="14"/>
-      <c r="B140" s="12"/>
-      <c r="C140" s="2"/>
-      <c r="D140" s="18"/>
-      <c r="E140" s="24"/>
-      <c r="F140" s="18"/>
-      <c r="G140" s="2"/>
-      <c r="H140" s="2"/>
+    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A140" s="14">
+        <v>8</v>
+      </c>
+      <c r="B140" s="12">
+        <v>20260831</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D140" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="E140" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="F140" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G140" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H140" s="2">
+        <v>24</v>
+      </c>
       <c r="I140" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J140" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K140" s="4">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M140" s="1"/>
       <c r="N140" s="1"/>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A141" s="14"/>
-      <c r="B141" s="12"/>
-      <c r="C141" s="2"/>
-      <c r="D141" s="18"/>
-      <c r="E141" s="24"/>
-      <c r="F141" s="18"/>
-      <c r="G141" s="2"/>
-      <c r="H141" s="2"/>
+    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A141" s="14">
+        <v>8</v>
+      </c>
+      <c r="B141" s="12">
+        <v>20260831</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D141" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E141" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="F141" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G141" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H141" s="2">
+        <v>27</v>
+      </c>
       <c r="I141" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J141" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K141" s="4">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A142" s="14"/>
-      <c r="B142" s="12"/>
-      <c r="C142" s="2"/>
-      <c r="D142" s="18"/>
-      <c r="E142" s="24"/>
-      <c r="F142" s="18"/>
-      <c r="G142" s="2"/>
-      <c r="H142" s="2"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A142" s="14">
+        <v>8</v>
+      </c>
+      <c r="B142" s="12">
+        <v>20260831</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D142" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E142" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="F142" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="G142" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H142" s="2">
+        <v>28</v>
+      </c>
       <c r="I142" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J142" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K142" s="4">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A143" s="14"/>
-      <c r="B143" s="12"/>
-      <c r="C143" s="2"/>
-      <c r="D143" s="18"/>
-      <c r="E143" s="24"/>
-      <c r="F143" s="18"/>
-      <c r="G143" s="2"/>
-      <c r="H143" s="2"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A143" s="14">
+        <v>8</v>
+      </c>
+      <c r="B143" s="12">
+        <v>20260831</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D143" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E143" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="F143" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="G143" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H143" s="2">
+        <v>29</v>
+      </c>
       <c r="I143" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J143" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K143" s="4">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A144" s="14"/>
-      <c r="B144" s="12"/>
-      <c r="C144" s="2"/>
-      <c r="D144" s="18"/>
-      <c r="E144" s="24"/>
-      <c r="F144" s="18"/>
-      <c r="G144" s="2"/>
-      <c r="H144" s="2"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="144" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A144" s="14">
+        <v>8</v>
+      </c>
+      <c r="B144" s="12">
+        <v>20260831</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D144" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E144" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="F144" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="G144" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H144" s="2">
+        <v>30</v>
+      </c>
       <c r="I144" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J144" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K144" s="4">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A145" s="14"/>
-      <c r="B145" s="12"/>
-      <c r="C145" s="2"/>
-      <c r="D145" s="18"/>
-      <c r="E145" s="24"/>
-      <c r="F145" s="18"/>
-      <c r="G145" s="2"/>
-      <c r="H145" s="2"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A145" s="14">
+        <v>8</v>
+      </c>
+      <c r="B145" s="12">
+        <v>20260831</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D145" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="E145" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="F145" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G145" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H145" s="2">
+        <v>30</v>
+      </c>
       <c r="I145" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J145" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K145" s="4">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A146" s="14"/>
-      <c r="B146" s="12"/>
-      <c r="C146" s="2"/>
-      <c r="D146" s="18"/>
-      <c r="E146" s="24"/>
-      <c r="F146" s="18"/>
-      <c r="G146" s="2"/>
-      <c r="H146" s="2"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A146" s="14">
+        <v>8</v>
+      </c>
+      <c r="B146" s="12">
+        <v>20260831</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D146" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="E146" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="F146" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="G146" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H146" s="2">
+        <v>32</v>
+      </c>
       <c r="I146" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J146" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K146" s="4">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A147" s="14"/>
-      <c r="B147" s="12"/>
-      <c r="C147" s="2"/>
-      <c r="D147" s="18"/>
-      <c r="E147" s="24"/>
-      <c r="F147" s="18"/>
-      <c r="G147" s="2"/>
-      <c r="H147" s="2"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A147" s="14">
+        <v>8</v>
+      </c>
+      <c r="B147" s="12">
+        <v>20260831</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D147" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E147" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="F147" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="G147" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H147" s="2">
+        <v>39</v>
+      </c>
       <c r="I147" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J147" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K147" s="4">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A148" s="14"/>
-      <c r="B148" s="12"/>
-      <c r="C148" s="2"/>
-      <c r="D148" s="18"/>
-      <c r="E148" s="24"/>
-      <c r="F148" s="18"/>
-      <c r="G148" s="2"/>
-      <c r="H148" s="2"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A148" s="14">
+        <v>8</v>
+      </c>
+      <c r="B148" s="12">
+        <v>20260831</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D148" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="E148" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="F148" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G148" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H148" s="2">
+        <v>43</v>
+      </c>
       <c r="I148" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J148" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K148" s="4">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A149" s="14"/>
-      <c r="B149" s="12"/>
-      <c r="C149" s="2"/>
-      <c r="D149" s="18"/>
-      <c r="E149" s="24"/>
-      <c r="F149" s="18"/>
-      <c r="G149" s="2"/>
-      <c r="H149" s="2"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A149" s="14">
+        <v>8</v>
+      </c>
+      <c r="B149" s="12">
+        <v>20260831</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D149" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E149" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="F149" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="G149" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H149" s="2">
+        <v>44</v>
+      </c>
       <c r="I149" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J149" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K149" s="4">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A150" s="14"/>
-      <c r="B150" s="12"/>
-      <c r="C150" s="2"/>
-      <c r="D150" s="18"/>
-      <c r="E150" s="24"/>
-      <c r="F150" s="18"/>
-      <c r="G150" s="2"/>
-      <c r="H150" s="2"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A150" s="14">
+        <v>8</v>
+      </c>
+      <c r="B150" s="12">
+        <v>20260831</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D150" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="E150" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="F150" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G150" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H150" s="2">
+        <v>49</v>
+      </c>
       <c r="I150" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J150" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K150" s="4">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A151" s="14"/>
-      <c r="B151" s="12"/>
-      <c r="C151" s="2"/>
-      <c r="D151" s="18"/>
-      <c r="E151" s="24"/>
-      <c r="F151" s="18"/>
-      <c r="G151" s="2"/>
-      <c r="H151" s="2"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A151" s="14">
+        <v>8</v>
+      </c>
+      <c r="B151" s="12">
+        <v>20260831</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D151" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E151" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="F151" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="G151" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H151" s="2">
+        <v>51</v>
+      </c>
       <c r="I151" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J151" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K151" s="4">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A152" s="14"/>
-      <c r="B152" s="12"/>
-      <c r="C152" s="2"/>
-      <c r="D152" s="18"/>
-      <c r="E152" s="24"/>
-      <c r="F152" s="18"/>
-      <c r="G152" s="2"/>
-      <c r="H152" s="2"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A152" s="14">
+        <v>8</v>
+      </c>
+      <c r="B152" s="12">
+        <v>20260831</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D152" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="E152" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="F152" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="G152" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H152" s="2">
+        <v>53</v>
+      </c>
       <c r="I152" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J152" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K152" s="4">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A153" s="14"/>
-      <c r="B153" s="12"/>
-      <c r="C153" s="2"/>
-      <c r="D153" s="18"/>
-      <c r="E153" s="24"/>
-      <c r="F153" s="18"/>
-      <c r="G153" s="2"/>
-      <c r="H153" s="2"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A153" s="14">
+        <v>8</v>
+      </c>
+      <c r="B153" s="12">
+        <v>20260831</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D153" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E153" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="F153" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="G153" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H153" s="2">
+        <v>56</v>
+      </c>
       <c r="I153" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J153" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K153" s="4">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A154" s="14"/>
-      <c r="B154" s="12"/>
-      <c r="C154" s="2"/>
-      <c r="D154" s="18"/>
-      <c r="E154" s="24"/>
-      <c r="F154" s="18"/>
-      <c r="G154" s="2"/>
-      <c r="H154" s="2"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A154" s="14">
+        <v>8</v>
+      </c>
+      <c r="B154" s="12">
+        <v>20260831</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D154" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="E154" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="F154" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G154" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H154" s="2">
+        <v>57</v>
+      </c>
       <c r="I154" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J154" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K154" s="4">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A155" s="14"/>
-      <c r="B155" s="12"/>
-      <c r="C155" s="2"/>
-      <c r="D155" s="18"/>
-      <c r="E155" s="24"/>
-      <c r="F155" s="18"/>
-      <c r="G155" s="2"/>
-      <c r="H155" s="2"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A155" s="14">
+        <v>8</v>
+      </c>
+      <c r="B155" s="12">
+        <v>20260831</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D155" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="E155" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="F155" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G155" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H155" s="2">
+        <v>61</v>
+      </c>
       <c r="I155" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J155" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K155" s="4">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A156" s="14"/>
-      <c r="B156" s="12"/>
-      <c r="C156" s="2"/>
-      <c r="D156" s="18"/>
-      <c r="E156" s="24"/>
-      <c r="F156" s="18"/>
-      <c r="G156" s="2"/>
-      <c r="H156" s="2"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A156" s="14">
+        <v>8</v>
+      </c>
+      <c r="B156" s="12">
+        <v>20260831</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D156" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="E156" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="F156" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="G156" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H156" s="2">
+        <v>62</v>
+      </c>
       <c r="I156" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J156" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K156" s="4">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A157" s="14"/>
       <c r="B157" s="12"/>
       <c r="C157" s="2"/>
@@ -6393,20 +6813,14 @@
       <c r="F157" s="18"/>
       <c r="G157" s="2"/>
       <c r="H157" s="2"/>
-      <c r="I157" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J157" s="2">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="I157" s="2"/>
+      <c r="J157" s="2"/>
       <c r="K157" s="4">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A158" s="14"/>
       <c r="B158" s="12"/>
       <c r="C158" s="2"/>
@@ -6415,20 +6829,14 @@
       <c r="F158" s="18"/>
       <c r="G158" s="2"/>
       <c r="H158" s="2"/>
-      <c r="I158" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J158" s="2">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="I158" s="2"/>
+      <c r="J158" s="2"/>
       <c r="K158" s="4">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A159" s="14"/>
       <c r="B159" s="12"/>
       <c r="C159" s="2"/>
@@ -6437,20 +6845,14 @@
       <c r="F159" s="18"/>
       <c r="G159" s="2"/>
       <c r="H159" s="2"/>
-      <c r="I159" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J159" s="2">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="I159" s="2"/>
+      <c r="J159" s="2"/>
       <c r="K159" s="4">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A160" s="14"/>
       <c r="B160" s="12"/>
       <c r="C160" s="2"/>
@@ -6459,20 +6861,14 @@
       <c r="F160" s="18"/>
       <c r="G160" s="2"/>
       <c r="H160" s="2"/>
-      <c r="I160" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J160" s="2">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="I160" s="2"/>
+      <c r="J160" s="2"/>
       <c r="K160" s="4">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A161" s="14"/>
       <c r="B161" s="12"/>
       <c r="C161" s="2"/>
@@ -6488,7 +6884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A162" s="14"/>
       <c r="B162" s="12"/>
       <c r="C162" s="2"/>
@@ -6504,7 +6900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163" s="14"/>
       <c r="B163" s="12"/>
       <c r="C163" s="2"/>
@@ -6520,7 +6916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A164" s="14"/>
       <c r="B164" s="12"/>
       <c r="C164" s="2"/>
@@ -6536,7 +6932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A165" s="14"/>
       <c r="B165" s="12"/>
       <c r="C165" s="2"/>
@@ -6552,7 +6948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A166" s="14"/>
       <c r="B166" s="12"/>
       <c r="C166" s="2"/>
@@ -6568,7 +6964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A167" s="14"/>
       <c r="B167" s="12"/>
       <c r="C167" s="2"/>
@@ -6584,7 +6980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A168" s="14"/>
       <c r="B168" s="12"/>
       <c r="C168" s="2"/>
@@ -6600,7 +6996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169" s="14"/>
       <c r="B169" s="12"/>
       <c r="C169" s="2"/>
@@ -6616,7 +7012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A170" s="14"/>
       <c r="B170" s="12"/>
       <c r="C170" s="2"/>
@@ -6632,7 +7028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A171" s="14"/>
       <c r="B171" s="12"/>
       <c r="C171" s="2"/>
@@ -6648,7 +7044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A172" s="14"/>
       <c r="B172" s="12"/>
       <c r="C172" s="2"/>
@@ -6664,7 +7060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A173" s="14"/>
       <c r="B173" s="12"/>
       <c r="C173" s="2"/>
@@ -6680,7 +7076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A174" s="14"/>
       <c r="B174" s="12"/>
       <c r="C174" s="2"/>
@@ -6696,7 +7092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A175" s="14"/>
       <c r="B175" s="12"/>
       <c r="C175" s="2"/>
@@ -6712,7 +7108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A176" s="14"/>
       <c r="B176" s="12"/>
       <c r="C176" s="2"/>
@@ -6728,7 +7124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A177" s="14"/>
       <c r="B177" s="12"/>
       <c r="C177" s="2"/>
@@ -6744,7 +7140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A178" s="14"/>
       <c r="B178" s="12"/>
       <c r="C178" s="2"/>
@@ -6760,7 +7156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A179" s="14"/>
       <c r="B179" s="12"/>
       <c r="C179" s="2"/>
@@ -6776,7 +7172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A180" s="14"/>
       <c r="B180" s="12"/>
       <c r="C180" s="2"/>
@@ -6792,7 +7188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A181" s="14"/>
       <c r="B181" s="12"/>
       <c r="C181" s="2"/>
@@ -6808,7 +7204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A182" s="14"/>
       <c r="B182" s="12"/>
       <c r="C182" s="2"/>
@@ -6824,7 +7220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A183" s="14"/>
       <c r="B183" s="12"/>
       <c r="C183" s="2"/>
@@ -6840,7 +7236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A184" s="14"/>
       <c r="B184" s="12"/>
       <c r="C184" s="2"/>
@@ -6856,7 +7252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A185" s="14"/>
       <c r="B185" s="12"/>
       <c r="C185" s="2"/>
@@ -6872,7 +7268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A186" s="14"/>
       <c r="B186" s="12"/>
       <c r="C186" s="2"/>
@@ -6888,7 +7284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A187" s="14"/>
       <c r="B187" s="12"/>
       <c r="C187" s="2"/>
@@ -6904,7 +7300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A188" s="14"/>
       <c r="B188" s="12"/>
       <c r="C188" s="2"/>
@@ -6920,7 +7316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A189" s="14"/>
       <c r="B189" s="12"/>
       <c r="C189" s="2"/>
@@ -6936,7 +7332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A190" s="14"/>
       <c r="B190" s="12"/>
       <c r="C190" s="2"/>
@@ -6952,7 +7348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A191" s="14"/>
       <c r="B191" s="12"/>
       <c r="C191" s="2"/>
@@ -6968,7 +7364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A192" s="14"/>
       <c r="B192" s="12"/>
       <c r="C192" s="2"/>
@@ -6984,7 +7380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A193" s="14"/>
       <c r="B193" s="12"/>
       <c r="C193" s="2"/>
@@ -7000,7 +7396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A194" s="14"/>
       <c r="B194" s="12"/>
       <c r="C194" s="2"/>
@@ -7016,7 +7412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A195" s="14"/>
       <c r="B195" s="12"/>
       <c r="C195" s="2"/>
@@ -7032,7 +7428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A196" s="14"/>
       <c r="B196" s="12"/>
       <c r="C196" s="2"/>
@@ -7048,7 +7444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A197" s="14"/>
       <c r="B197" s="12"/>
       <c r="C197" s="2"/>
@@ -7064,7 +7460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A198" s="14"/>
       <c r="B198" s="12"/>
       <c r="C198" s="2"/>
@@ -7080,7 +7476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A199" s="14"/>
       <c r="B199" s="12"/>
       <c r="C199" s="2"/>
@@ -7096,7 +7492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="14"/>
       <c r="B200" s="12"/>
       <c r="C200" s="2"/>
@@ -7112,7 +7508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A201" s="14"/>
       <c r="B201" s="12"/>
       <c r="C201" s="2"/>
@@ -7128,7 +7524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A202" s="14"/>
       <c r="B202" s="12"/>
       <c r="C202" s="2"/>
@@ -7144,7 +7540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A203" s="14"/>
       <c r="B203" s="12"/>
       <c r="C203" s="2"/>
@@ -7160,7 +7556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A204" s="14"/>
       <c r="B204" s="12"/>
       <c r="C204" s="2"/>
@@ -7176,7 +7572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A205" s="14"/>
       <c r="B205" s="12"/>
       <c r="C205" s="2"/>
@@ -7192,7 +7588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A206" s="14"/>
       <c r="B206" s="12"/>
       <c r="C206" s="2"/>
@@ -7208,7 +7604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A207" s="14"/>
       <c r="B207" s="12"/>
       <c r="C207" s="2"/>
@@ -7224,7 +7620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A208" s="14"/>
       <c r="B208" s="12"/>
       <c r="C208" s="2"/>
@@ -7240,7 +7636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A209" s="14"/>
       <c r="B209" s="12"/>
       <c r="C209" s="2"/>
@@ -7256,7 +7652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A210" s="14"/>
       <c r="B210" s="12"/>
       <c r="C210" s="2"/>
@@ -7272,7 +7668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A211" s="14"/>
       <c r="B211" s="12"/>
       <c r="C211" s="2"/>
@@ -7288,7 +7684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A212" s="14"/>
       <c r="B212" s="12"/>
       <c r="C212" s="2"/>
@@ -7304,7 +7700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A213" s="14"/>
       <c r="B213" s="12"/>
       <c r="C213" s="2"/>
@@ -7320,7 +7716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A214" s="14"/>
       <c r="B214" s="12"/>
       <c r="C214" s="2"/>
@@ -7336,7 +7732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A215" s="14"/>
       <c r="B215" s="12"/>
       <c r="C215" s="2"/>
@@ -7352,7 +7748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A216" s="14"/>
       <c r="B216" s="12"/>
       <c r="C216" s="2"/>
@@ -7368,7 +7764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A217" s="14"/>
       <c r="B217" s="12"/>
       <c r="C217" s="2"/>
@@ -7384,7 +7780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A218" s="14"/>
       <c r="B218" s="12"/>
       <c r="C218" s="2"/>
@@ -7400,7 +7796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A219" s="14"/>
       <c r="B219" s="12"/>
       <c r="C219" s="2"/>
@@ -7416,7 +7812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A220" s="14"/>
       <c r="B220" s="12"/>
       <c r="C220" s="2"/>
@@ -7432,7 +7828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A221" s="14"/>
       <c r="B221" s="12"/>
       <c r="C221" s="2"/>
@@ -7448,7 +7844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A222" s="14"/>
       <c r="B222" s="12"/>
       <c r="C222" s="2"/>
@@ -7464,7 +7860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A223" s="14"/>
       <c r="B223" s="12"/>
       <c r="C223" s="2"/>
@@ -7480,7 +7876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A224" s="14"/>
       <c r="B224" s="12"/>
       <c r="C224" s="2"/>
@@ -7496,7 +7892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A225" s="14"/>
       <c r="B225" s="12"/>
       <c r="C225" s="2"/>
@@ -7512,7 +7908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A226" s="14"/>
       <c r="B226" s="12"/>
       <c r="C226" s="2"/>
@@ -7528,7 +7924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A227" s="14"/>
       <c r="B227" s="12"/>
       <c r="C227" s="2"/>
@@ -7544,7 +7940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A228" s="14"/>
       <c r="B228" s="12"/>
       <c r="C228" s="2"/>
@@ -7560,7 +7956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A229" s="14"/>
       <c r="B229" s="12"/>
       <c r="C229" s="2"/>
@@ -7576,7 +7972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A230" s="14"/>
       <c r="B230" s="12"/>
       <c r="C230" s="2"/>
@@ -7592,7 +7988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A231" s="14"/>
       <c r="B231" s="12"/>
       <c r="C231" s="2"/>
@@ -7608,7 +8004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A232" s="14"/>
       <c r="B232" s="12"/>
       <c r="C232" s="2"/>
@@ -7624,7 +8020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A233" s="14"/>
       <c r="B233" s="12"/>
       <c r="C233" s="2"/>
@@ -7640,7 +8036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A234" s="14"/>
       <c r="B234" s="12"/>
       <c r="C234" s="2"/>
@@ -7656,7 +8052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A235" s="14"/>
       <c r="B235" s="12"/>
       <c r="C235" s="2"/>
@@ -7672,7 +8068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A236" s="14"/>
       <c r="B236" s="12"/>
       <c r="C236" s="2"/>
@@ -7688,7 +8084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A237" s="14"/>
       <c r="B237" s="12"/>
       <c r="C237" s="2"/>
@@ -7704,7 +8100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A238" s="14"/>
       <c r="B238" s="12"/>
       <c r="C238" s="2"/>
@@ -7720,7 +8116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A239" s="14"/>
       <c r="B239" s="12"/>
       <c r="C239" s="2"/>
@@ -7736,7 +8132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A240" s="14"/>
       <c r="B240" s="12"/>
       <c r="C240" s="2"/>
@@ -7752,7 +8148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A241" s="14"/>
       <c r="B241" s="12"/>
       <c r="C241" s="2"/>
@@ -7768,7 +8164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A242" s="14"/>
       <c r="B242" s="12"/>
       <c r="C242" s="2"/>
@@ -7784,7 +8180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A243" s="14"/>
       <c r="B243" s="12"/>
       <c r="C243" s="2"/>
@@ -7800,7 +8196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A244" s="14"/>
       <c r="B244" s="12"/>
       <c r="C244" s="2"/>
@@ -7816,7 +8212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A245" s="14"/>
       <c r="B245" s="12"/>
       <c r="C245" s="2"/>
@@ -7832,7 +8228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A246" s="14"/>
       <c r="B246" s="12"/>
       <c r="C246" s="2"/>
@@ -7848,7 +8244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A247" s="14"/>
       <c r="B247" s="12"/>
       <c r="C247" s="2"/>
@@ -7864,7 +8260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A248" s="14"/>
       <c r="B248" s="12"/>
       <c r="C248" s="2"/>
@@ -7880,7 +8276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A249" s="14"/>
       <c r="B249" s="12"/>
       <c r="C249" s="2"/>
@@ -7896,7 +8292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A250" s="14"/>
       <c r="B250" s="12"/>
       <c r="C250" s="2"/>
@@ -7912,7 +8308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A251" s="14"/>
       <c r="B251" s="12"/>
       <c r="C251" s="2"/>
@@ -7928,7 +8324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A252" s="14"/>
       <c r="B252" s="12"/>
       <c r="C252" s="2"/>
@@ -7944,7 +8340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A253" s="14"/>
       <c r="B253" s="12"/>
       <c r="C253" s="2"/>
@@ -7960,7 +8356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A254" s="14"/>
       <c r="B254" s="12"/>
       <c r="C254" s="2"/>
@@ -7976,7 +8372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A255" s="14"/>
       <c r="B255" s="12"/>
       <c r="C255" s="2"/>
@@ -7992,7 +8388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A256" s="30"/>
       <c r="B256" s="31"/>
       <c r="C256" s="32"/>
@@ -8008,7 +8404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A257" s="30"/>
       <c r="B257" s="31"/>
       <c r="C257" s="32"/>
@@ -8024,7 +8420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A258" s="30"/>
       <c r="B258" s="31"/>
       <c r="C258" s="32"/>
@@ -8040,7 +8436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A259" s="30"/>
       <c r="B259" s="31"/>
       <c r="C259" s="32"/>
@@ -8056,7 +8452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A260" s="30"/>
       <c r="B260" s="31"/>
       <c r="C260" s="32"/>
@@ -8072,7 +8468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A261" s="30"/>
       <c r="B261" s="31"/>
       <c r="C261" s="32"/>
@@ -8088,7 +8484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A262" s="30"/>
       <c r="B262" s="31"/>
       <c r="C262" s="32"/>
@@ -8104,7 +8500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A263" s="30"/>
       <c r="B263" s="31"/>
       <c r="C263" s="32"/>
@@ -8120,7 +8516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A264" s="30"/>
       <c r="B264" s="31"/>
       <c r="C264" s="32"/>
@@ -8136,7 +8532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A265" s="30"/>
       <c r="B265" s="31"/>
       <c r="C265" s="32"/>
@@ -8152,7 +8548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A266" s="30"/>
       <c r="B266" s="31"/>
       <c r="C266" s="32"/>
@@ -8168,7 +8564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A267" s="30"/>
       <c r="B267" s="31"/>
       <c r="C267" s="32"/>
@@ -8184,7 +8580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A268" s="30"/>
       <c r="B268" s="31"/>
       <c r="C268" s="32"/>
@@ -8200,7 +8596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A269" s="30"/>
       <c r="B269" s="31"/>
       <c r="C269" s="32"/>
@@ -8216,7 +8612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A270" s="30"/>
       <c r="B270" s="31"/>
       <c r="C270" s="32"/>
@@ -8232,7 +8628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A271" s="30"/>
       <c r="B271" s="31"/>
       <c r="C271" s="32"/>
@@ -8248,7 +8644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A272" s="30"/>
       <c r="B272" s="31"/>
       <c r="C272" s="32"/>
@@ -8264,7 +8660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A273" s="30"/>
       <c r="B273" s="31"/>
       <c r="C273" s="32"/>
@@ -8280,7 +8676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A274" s="30"/>
       <c r="B274" s="31"/>
       <c r="C274" s="32"/>
@@ -8296,7 +8692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A275" s="30"/>
       <c r="B275" s="31"/>
       <c r="C275" s="32"/>
@@ -8312,7 +8708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A276" s="30"/>
       <c r="B276" s="31"/>
       <c r="C276" s="32"/>
@@ -8328,7 +8724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A277" s="30"/>
       <c r="B277" s="31"/>
       <c r="C277" s="32"/>
@@ -8344,7 +8740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A278" s="30"/>
       <c r="B278" s="31"/>
       <c r="C278" s="32"/>
@@ -8360,7 +8756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A279" s="30"/>
       <c r="B279" s="31"/>
       <c r="C279" s="32"/>
@@ -8376,7 +8772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A280" s="30"/>
       <c r="B280" s="31"/>
       <c r="C280" s="32"/>
@@ -8392,7 +8788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A281" s="30"/>
       <c r="B281" s="31"/>
       <c r="C281" s="32"/>
@@ -8408,7 +8804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A282" s="30"/>
       <c r="B282" s="31"/>
       <c r="C282" s="32"/>
@@ -8424,7 +8820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A283" s="30"/>
       <c r="B283" s="31"/>
       <c r="C283" s="32"/>
@@ -8440,7 +8836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A284" s="30"/>
       <c r="B284" s="31"/>
       <c r="C284" s="32"/>
@@ -8456,7 +8852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A285" s="30"/>
       <c r="B285" s="31"/>
       <c r="C285" s="32"/>
@@ -8472,7 +8868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A286" s="30"/>
       <c r="B286" s="31"/>
       <c r="C286" s="32"/>
@@ -8488,7 +8884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A287" s="30"/>
       <c r="B287" s="31"/>
       <c r="C287" s="32"/>
@@ -8504,7 +8900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A288" s="30"/>
       <c r="B288" s="31"/>
       <c r="C288" s="32"/>
@@ -8520,7 +8916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A289" s="30"/>
       <c r="B289" s="31"/>
       <c r="C289" s="32"/>
@@ -8536,7 +8932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A290" s="30"/>
       <c r="B290" s="31"/>
       <c r="C290" s="32"/>
@@ -8552,7 +8948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A291" s="30"/>
       <c r="B291" s="31"/>
       <c r="C291" s="32"/>
@@ -8568,7 +8964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A292" s="30"/>
       <c r="B292" s="31"/>
       <c r="C292" s="32"/>
@@ -8584,7 +8980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A293" s="30"/>
       <c r="B293" s="31"/>
       <c r="C293" s="32"/>
@@ -8600,7 +8996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A294" s="30"/>
       <c r="B294" s="31"/>
       <c r="C294" s="32"/>
@@ -8616,7 +9012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A295" s="30"/>
       <c r="B295" s="31"/>
       <c r="C295" s="32"/>
@@ -8632,7 +9028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A296" s="30"/>
       <c r="B296" s="31"/>
       <c r="C296" s="32"/>
@@ -8648,7 +9044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A297" s="30"/>
       <c r="B297" s="31"/>
       <c r="C297" s="32"/>
@@ -8664,7 +9060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A298" s="30"/>
       <c r="B298" s="31"/>
       <c r="C298" s="32"/>
@@ -8680,7 +9076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A299" s="30"/>
       <c r="B299" s="31"/>
       <c r="C299" s="32"/>
@@ -8696,7 +9092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A300" s="30"/>
       <c r="B300" s="31"/>
       <c r="C300" s="32"/>
@@ -8712,7 +9108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A301" s="30"/>
       <c r="B301" s="31"/>
       <c r="C301" s="32"/>
@@ -8728,7 +9124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A302" s="30"/>
       <c r="B302" s="31"/>
       <c r="C302" s="32"/>
@@ -8744,7 +9140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A303" s="30"/>
       <c r="B303" s="31"/>
       <c r="C303" s="32"/>
@@ -8760,7 +9156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A304" s="30"/>
       <c r="B304" s="31"/>
       <c r="C304" s="32"/>
@@ -8776,7 +9172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A305" s="30"/>
       <c r="B305" s="31"/>
       <c r="C305" s="32"/>
@@ -8792,7 +9188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A306" s="30"/>
       <c r="B306" s="31"/>
       <c r="C306" s="32"/>
@@ -8808,7 +9204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A307" s="30"/>
       <c r="B307" s="31"/>
       <c r="C307" s="32"/>
@@ -8824,7 +9220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A308" s="30"/>
       <c r="B308" s="31"/>
       <c r="C308" s="32"/>
@@ -8840,7 +9236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A309" s="30"/>
       <c r="B309" s="31"/>
       <c r="C309" s="32"/>
@@ -8856,7 +9252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A310" s="30"/>
       <c r="B310" s="31"/>
       <c r="C310" s="32"/>
@@ -8872,7 +9268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A311" s="30"/>
       <c r="B311" s="31"/>
       <c r="C311" s="32"/>
@@ -8888,7 +9284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A312" s="30"/>
       <c r="B312" s="31"/>
       <c r="C312" s="32"/>
@@ -8904,7 +9300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A313" s="30"/>
       <c r="B313" s="31"/>
       <c r="C313" s="32"/>
@@ -8920,7 +9316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A314" s="30"/>
       <c r="B314" s="31"/>
       <c r="C314" s="32"/>
@@ -8936,7 +9332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A315" s="30"/>
       <c r="B315" s="31"/>
       <c r="C315" s="32"/>
@@ -8952,7 +9348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A316" s="30"/>
       <c r="B316" s="31"/>
       <c r="C316" s="32"/>
@@ -8968,7 +9364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A317" s="30"/>
       <c r="B317" s="31"/>
       <c r="C317" s="32"/>
@@ -8984,7 +9380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A318" s="30"/>
       <c r="B318" s="31"/>
       <c r="C318" s="32"/>
@@ -9000,7 +9396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A319" s="30"/>
       <c r="B319" s="31"/>
       <c r="C319" s="32"/>
@@ -9016,7 +9412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A320" s="30"/>
       <c r="B320" s="31"/>
       <c r="C320" s="32"/>
@@ -9032,7 +9428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A321" s="30"/>
       <c r="B321" s="31"/>
       <c r="C321" s="32"/>
@@ -9048,7 +9444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A322" s="30"/>
       <c r="B322" s="31"/>
       <c r="C322" s="32"/>
@@ -9064,7 +9460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A323" s="30"/>
       <c r="B323" s="31"/>
       <c r="C323" s="32"/>
@@ -9080,7 +9476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A324" s="30"/>
       <c r="B324" s="31"/>
       <c r="C324" s="32"/>
@@ -9096,7 +9492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A325" s="30"/>
       <c r="B325" s="31"/>
       <c r="C325" s="32"/>
@@ -9112,7 +9508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A326" s="30"/>
       <c r="B326" s="31"/>
       <c r="C326" s="32"/>
@@ -9128,7 +9524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A327" s="30"/>
       <c r="B327" s="31"/>
       <c r="C327" s="32"/>
@@ -9144,7 +9540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A328" s="30"/>
       <c r="B328" s="31"/>
       <c r="C328" s="32"/>
@@ -9160,7 +9556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A329" s="30"/>
       <c r="B329" s="31"/>
       <c r="C329" s="32"/>
@@ -9176,7 +9572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A330" s="30"/>
       <c r="B330" s="31"/>
       <c r="C330" s="32"/>
@@ -9192,7 +9588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A331" s="30"/>
       <c r="B331" s="31"/>
       <c r="C331" s="32"/>
@@ -9208,7 +9604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A332" s="30"/>
       <c r="B332" s="31"/>
       <c r="C332" s="32"/>
@@ -9224,7 +9620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A333" s="30"/>
       <c r="B333" s="31"/>
       <c r="C333" s="32"/>
@@ -9240,7 +9636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A334" s="30"/>
       <c r="B334" s="31"/>
       <c r="C334" s="32"/>
@@ -9256,7 +9652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A335" s="30"/>
       <c r="B335" s="31"/>
       <c r="C335" s="32"/>
@@ -9272,7 +9668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A336" s="30"/>
       <c r="B336" s="31"/>
       <c r="C336" s="32"/>
@@ -9288,7 +9684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A337" s="30"/>
       <c r="B337" s="31"/>
       <c r="C337" s="32"/>
@@ -9304,7 +9700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A338" s="30"/>
       <c r="B338" s="31"/>
       <c r="C338" s="32"/>
@@ -9320,7 +9716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A339" s="30"/>
       <c r="B339" s="31"/>
       <c r="C339" s="32"/>
@@ -9336,7 +9732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A340" s="30"/>
       <c r="B340" s="31"/>
       <c r="C340" s="32"/>
@@ -9352,7 +9748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A341" s="30"/>
       <c r="B341" s="31"/>
       <c r="C341" s="32"/>
@@ -9368,7 +9764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A342" s="30"/>
       <c r="B342" s="31"/>
       <c r="C342" s="32"/>
@@ -9384,7 +9780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A343" s="30"/>
       <c r="B343" s="31"/>
       <c r="C343" s="32"/>
@@ -9400,7 +9796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A344" s="30"/>
       <c r="B344" s="31"/>
       <c r="C344" s="32"/>
@@ -9416,7 +9812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A345" s="30"/>
       <c r="B345" s="31"/>
       <c r="C345" s="32"/>
@@ -9432,7 +9828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A346" s="30"/>
       <c r="B346" s="31"/>
       <c r="C346" s="32"/>
@@ -9448,7 +9844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A347" s="30"/>
       <c r="B347" s="31"/>
       <c r="C347" s="32"/>
@@ -9464,7 +9860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A348" s="30"/>
       <c r="B348" s="31"/>
       <c r="C348" s="32"/>
@@ -9480,7 +9876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A349" s="30"/>
       <c r="B349" s="31"/>
       <c r="C349" s="32"/>
@@ -9496,7 +9892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A350" s="30"/>
       <c r="B350" s="31"/>
       <c r="C350" s="32"/>
@@ -9512,7 +9908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A351" s="30"/>
       <c r="B351" s="31"/>
       <c r="C351" s="32"/>
@@ -9528,7 +9924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A352" s="30"/>
       <c r="B352" s="31"/>
       <c r="C352" s="32"/>
@@ -9544,7 +9940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A353" s="30"/>
       <c r="B353" s="31"/>
       <c r="C353" s="32"/>
@@ -9560,7 +9956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="354" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A354" s="30"/>
       <c r="B354" s="31"/>
       <c r="C354" s="32"/>
@@ -9576,7 +9972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A355" s="30"/>
       <c r="B355" s="31"/>
       <c r="C355" s="32"/>
@@ -9592,7 +9988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="356" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A356" s="30"/>
       <c r="B356" s="31"/>
       <c r="C356" s="32"/>
@@ -9608,7 +10004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="357" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A357" s="30"/>
       <c r="B357" s="31"/>
       <c r="C357" s="32"/>
@@ -9624,7 +10020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="358" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A358" s="30"/>
       <c r="B358" s="31"/>
       <c r="C358" s="32"/>
@@ -9640,7 +10036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="359" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A359" s="30"/>
       <c r="B359" s="31"/>
       <c r="C359" s="32"/>
@@ -9656,7 +10052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="360" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A360" s="30"/>
       <c r="B360" s="31"/>
       <c r="C360" s="32"/>
@@ -9672,7 +10068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A361" s="30"/>
       <c r="B361" s="31"/>
       <c r="C361" s="32"/>
@@ -9688,7 +10084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A362" s="30"/>
       <c r="B362" s="31"/>
       <c r="C362" s="32"/>
@@ -9704,7 +10100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A363" s="30"/>
       <c r="B363" s="31"/>
       <c r="C363" s="32"/>
@@ -9720,7 +10116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="364" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A364" s="30"/>
       <c r="B364" s="31"/>
       <c r="C364" s="32"/>
@@ -9736,7 +10132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="365" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A365" s="30"/>
       <c r="B365" s="31"/>
       <c r="C365" s="32"/>
@@ -9752,7 +10148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="366" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A366" s="30"/>
       <c r="B366" s="31"/>
       <c r="C366" s="32"/>
@@ -9768,7 +10164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="367" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A367" s="30"/>
       <c r="B367" s="31"/>
       <c r="C367" s="32"/>
@@ -9784,7 +10180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A368" s="30"/>
       <c r="B368" s="31"/>
       <c r="C368" s="32"/>
@@ -9800,7 +10196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A369" s="30"/>
       <c r="B369" s="31"/>
       <c r="C369" s="32"/>
@@ -9816,7 +10212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="370" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A370" s="30"/>
       <c r="B370" s="31"/>
       <c r="C370" s="32"/>
@@ -9832,7 +10228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="371" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A371" s="30"/>
       <c r="B371" s="31"/>
       <c r="C371" s="32"/>
@@ -9848,7 +10244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="372" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A372" s="30"/>
       <c r="B372" s="31"/>
       <c r="C372" s="32"/>
@@ -9864,7 +10260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="373" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A373" s="30"/>
       <c r="B373" s="31"/>
       <c r="C373" s="32"/>
@@ -9880,7 +10276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="374" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A374" s="30"/>
       <c r="B374" s="31"/>
       <c r="C374" s="32"/>
@@ -9896,7 +10292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="375" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A375" s="30"/>
       <c r="B375" s="31"/>
       <c r="C375" s="32"/>
@@ -9912,7 +10308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="376" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A376" s="30"/>
       <c r="B376" s="31"/>
       <c r="C376" s="32"/>
@@ -9928,7 +10324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="377" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A377" s="30"/>
       <c r="B377" s="31"/>
       <c r="C377" s="32"/>
@@ -9944,7 +10340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="378" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A378" s="30"/>
       <c r="B378" s="31"/>
       <c r="C378" s="32"/>
@@ -9960,7 +10356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="379" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A379" s="30"/>
       <c r="B379" s="31"/>
       <c r="C379" s="32"/>
@@ -9976,7 +10372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="380" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A380" s="30"/>
       <c r="B380" s="31"/>
       <c r="C380" s="32"/>
@@ -9992,7 +10388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="381" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A381" s="30"/>
       <c r="B381" s="31"/>
       <c r="C381" s="32"/>
@@ -10008,7 +10404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="382" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A382" s="30"/>
       <c r="B382" s="31"/>
       <c r="C382" s="32"/>
@@ -10024,7 +10420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="383" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A383" s="30"/>
       <c r="B383" s="31"/>
       <c r="C383" s="32"/>
@@ -10040,7 +10436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="384" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A384" s="30"/>
       <c r="B384" s="31"/>
       <c r="C384" s="32"/>
@@ -10056,7 +10452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="385" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A385" s="30"/>
       <c r="B385" s="31"/>
       <c r="C385" s="32"/>
@@ -10072,7 +10468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="386" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A386" s="30"/>
       <c r="B386" s="31"/>
       <c r="C386" s="32"/>
@@ -10088,7 +10484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="387" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A387" s="30"/>
       <c r="B387" s="31"/>
       <c r="C387" s="32"/>
@@ -10104,7 +10500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="388" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A388" s="30"/>
       <c r="B388" s="31"/>
       <c r="C388" s="32"/>
@@ -10120,7 +10516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="389" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A389" s="30"/>
       <c r="B389" s="31"/>
       <c r="C389" s="32"/>
@@ -10136,7 +10532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="390" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A390" s="30"/>
       <c r="B390" s="31"/>
       <c r="C390" s="32"/>
@@ -10152,7 +10548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="391" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A391" s="30"/>
       <c r="B391" s="31"/>
       <c r="C391" s="32"/>
@@ -10168,7 +10564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="392" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A392" s="30"/>
       <c r="B392" s="31"/>
       <c r="C392" s="32"/>
@@ -10184,7 +10580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="393" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A393" s="30"/>
       <c r="B393" s="31"/>
       <c r="C393" s="32"/>
@@ -10200,7 +10596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="394" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A394" s="30"/>
       <c r="B394" s="31"/>
       <c r="C394" s="32"/>
@@ -10216,7 +10612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="395" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A395" s="30"/>
       <c r="B395" s="31"/>
       <c r="C395" s="32"/>
@@ -10232,7 +10628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="396" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A396" s="30"/>
       <c r="B396" s="31"/>
       <c r="C396" s="32"/>
@@ -10248,7 +10644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="397" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A397" s="30"/>
       <c r="B397" s="31"/>
       <c r="C397" s="32"/>
@@ -10264,7 +10660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="398" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A398" s="30"/>
       <c r="B398" s="31"/>
       <c r="C398" s="32"/>
@@ -10280,7 +10676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="399" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A399" s="30"/>
       <c r="B399" s="31"/>
       <c r="C399" s="32"/>
@@ -10296,7 +10692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="400" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A400" s="30"/>
       <c r="B400" s="31"/>
       <c r="C400" s="32"/>
@@ -10312,7 +10708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="401" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A401" s="30"/>
       <c r="B401" s="31"/>
       <c r="C401" s="32"/>
@@ -10328,7 +10724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="402" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A402" s="30"/>
       <c r="B402" s="31"/>
       <c r="C402" s="32"/>
@@ -10344,7 +10740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="403" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A403" s="30"/>
       <c r="B403" s="31"/>
       <c r="C403" s="32"/>
@@ -10360,7 +10756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="404" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A404" s="30"/>
       <c r="B404" s="31"/>
       <c r="C404" s="32"/>
@@ -10376,7 +10772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="405" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A405" s="30"/>
       <c r="B405" s="31"/>
       <c r="C405" s="32"/>
@@ -10392,7 +10788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="406" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A406" s="30"/>
       <c r="B406" s="31"/>
       <c r="C406" s="32"/>
@@ -10408,7 +10804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="407" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A407" s="30"/>
       <c r="B407" s="31"/>
       <c r="C407" s="32"/>
@@ -10424,7 +10820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="408" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A408" s="30"/>
       <c r="B408" s="31"/>
       <c r="C408" s="32"/>
@@ -10440,7 +10836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="409" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A409" s="30"/>
       <c r="B409" s="31"/>
       <c r="C409" s="32"/>
@@ -10456,7 +10852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="410" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A410" s="30"/>
       <c r="B410" s="31"/>
       <c r="C410" s="32"/>
@@ -10472,7 +10868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="411" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A411" s="30"/>
       <c r="B411" s="31"/>
       <c r="C411" s="32"/>
@@ -10488,7 +10884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="412" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A412" s="30"/>
       <c r="B412" s="31"/>
       <c r="C412" s="32"/>
@@ -10504,7 +10900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="413" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A413" s="30"/>
       <c r="B413" s="31"/>
       <c r="C413" s="32"/>
@@ -10520,7 +10916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="414" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A414" s="30"/>
       <c r="B414" s="31"/>
       <c r="C414" s="32"/>
@@ -10536,7 +10932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="415" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A415" s="30"/>
       <c r="B415" s="31"/>
       <c r="C415" s="32"/>
@@ -10552,7 +10948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="416" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A416" s="30"/>
       <c r="B416" s="31"/>
       <c r="C416" s="32"/>
@@ -10568,7 +10964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="417" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A417" s="30"/>
       <c r="B417" s="31"/>
       <c r="C417" s="32"/>
@@ -10584,7 +10980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="418" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A418" s="30"/>
       <c r="B418" s="31"/>
       <c r="C418" s="32"/>
@@ -10600,7 +10996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="419" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A419" s="30"/>
       <c r="B419" s="31"/>
       <c r="C419" s="32"/>
@@ -10616,7 +11012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="420" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A420" s="30"/>
       <c r="B420" s="31"/>
       <c r="C420" s="32"/>
@@ -10632,7 +11028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="421" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A421" s="30"/>
       <c r="B421" s="31"/>
       <c r="C421" s="32"/>
@@ -10648,7 +11044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="422" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A422" s="30"/>
       <c r="B422" s="31"/>
       <c r="C422" s="32"/>
@@ -10664,7 +11060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="423" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A423" s="30"/>
       <c r="B423" s="31"/>
       <c r="C423" s="32"/>
@@ -10680,7 +11076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="424" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A424" s="30"/>
       <c r="B424" s="31"/>
       <c r="C424" s="32"/>
@@ -10696,7 +11092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="425" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A425" s="30"/>
       <c r="B425" s="31"/>
       <c r="C425" s="32"/>
@@ -10712,7 +11108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="426" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A426" s="30"/>
       <c r="B426" s="31"/>
       <c r="C426" s="32"/>
@@ -10728,7 +11124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="427" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A427" s="30"/>
       <c r="B427" s="31"/>
       <c r="C427" s="32"/>
@@ -10744,7 +11140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="428" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A428" s="30"/>
       <c r="B428" s="31"/>
       <c r="C428" s="32"/>
@@ -10760,7 +11156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="429" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A429" s="30"/>
       <c r="B429" s="31"/>
       <c r="C429" s="32"/>
@@ -10776,7 +11172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="430" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A430" s="30"/>
       <c r="B430" s="31"/>
       <c r="C430" s="32"/>
@@ -10792,7 +11188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="431" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A431" s="30"/>
       <c r="B431" s="31"/>
       <c r="C431" s="32"/>
@@ -10808,7 +11204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="432" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A432" s="30"/>
       <c r="B432" s="31"/>
       <c r="C432" s="32"/>
@@ -10824,7 +11220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="433" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A433" s="30"/>
       <c r="B433" s="31"/>
       <c r="C433" s="32"/>
@@ -10840,7 +11236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="434" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A434" s="30"/>
       <c r="B434" s="31"/>
       <c r="C434" s="32"/>
@@ -10856,7 +11252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="435" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A435" s="30"/>
       <c r="B435" s="31"/>
       <c r="C435" s="32"/>
@@ -10872,7 +11268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="436" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A436" s="30"/>
       <c r="B436" s="31"/>
       <c r="C436" s="32"/>
@@ -10888,7 +11284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="437" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A437" s="30"/>
       <c r="B437" s="31"/>
       <c r="C437" s="32"/>
@@ -10904,7 +11300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="438" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A438" s="30"/>
       <c r="B438" s="31"/>
       <c r="C438" s="32"/>
@@ -10920,7 +11316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="439" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A439" s="30"/>
       <c r="B439" s="31"/>
       <c r="C439" s="32"/>
@@ -10936,7 +11332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="440" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A440" s="30"/>
       <c r="B440" s="31"/>
       <c r="C440" s="32"/>
@@ -10952,7 +11348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="441" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A441" s="30"/>
       <c r="B441" s="31"/>
       <c r="C441" s="32"/>
@@ -10968,7 +11364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="442" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A442" s="30"/>
       <c r="B442" s="31"/>
       <c r="C442" s="32"/>
@@ -10984,7 +11380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="443" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A443" s="30"/>
       <c r="B443" s="31"/>
       <c r="C443" s="32"/>
@@ -11000,7 +11396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="444" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A444" s="30"/>
       <c r="B444" s="31"/>
       <c r="C444" s="32"/>
@@ -11016,7 +11412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="445" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A445" s="30"/>
       <c r="B445" s="31"/>
       <c r="C445" s="32"/>
@@ -11032,7 +11428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="446" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A446" s="30"/>
       <c r="B446" s="31"/>
       <c r="C446" s="32"/>
@@ -11048,7 +11444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="447" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A447" s="30"/>
       <c r="B447" s="31"/>
       <c r="C447" s="32"/>
@@ -11064,7 +11460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="448" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A448" s="30"/>
       <c r="B448" s="31"/>
       <c r="C448" s="32"/>
@@ -11080,7 +11476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="449" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A449" s="30"/>
       <c r="B449" s="31"/>
       <c r="C449" s="32"/>
@@ -11096,7 +11492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="450" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A450" s="30"/>
       <c r="B450" s="31"/>
       <c r="C450" s="32"/>
@@ -11112,7 +11508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="451" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A451" s="30"/>
       <c r="B451" s="31"/>
       <c r="C451" s="32"/>
@@ -11128,7 +11524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="452" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A452" s="30"/>
       <c r="B452" s="31"/>
       <c r="C452" s="32"/>
@@ -11144,7 +11540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="453" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A453" s="30"/>
       <c r="B453" s="31"/>
       <c r="C453" s="32"/>
@@ -11160,7 +11556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="454" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A454" s="30"/>
       <c r="B454" s="12"/>
       <c r="C454" s="32"/>
@@ -11176,7 +11572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="455" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A455" s="30"/>
       <c r="B455" s="12"/>
       <c r="C455" s="32"/>
@@ -11192,7 +11588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="456" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A456" s="30"/>
       <c r="B456" s="12"/>
       <c r="C456" s="32"/>
@@ -11208,7 +11604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="457" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A457" s="30"/>
       <c r="B457" s="12"/>
       <c r="C457" s="32"/>
@@ -11224,7 +11620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="458" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A458" s="30"/>
       <c r="B458" s="12"/>
       <c r="C458" s="32"/>
@@ -11240,7 +11636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="459" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A459" s="30"/>
       <c r="B459" s="12"/>
       <c r="C459" s="32"/>
@@ -11256,7 +11652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="460" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A460" s="30"/>
       <c r="B460" s="12"/>
       <c r="C460" s="32"/>
@@ -11272,7 +11668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="461" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A461" s="30"/>
       <c r="B461" s="12"/>
       <c r="C461" s="32"/>
@@ -11288,7 +11684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="462" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A462" s="30"/>
       <c r="B462" s="12"/>
       <c r="C462" s="32"/>
@@ -11304,7 +11700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="463" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A463" s="30"/>
       <c r="B463" s="12"/>
       <c r="C463" s="32"/>
@@ -11320,7 +11716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="464" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A464" s="30"/>
       <c r="B464" s="12"/>
       <c r="C464" s="32"/>
@@ -11336,7 +11732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="465" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A465" s="30"/>
       <c r="B465" s="12"/>
       <c r="C465" s="32"/>
@@ -11352,7 +11748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="466" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A466" s="30"/>
       <c r="B466" s="12"/>
       <c r="C466" s="32"/>
@@ -11368,7 +11764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="467" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A467" s="30"/>
       <c r="B467" s="12"/>
       <c r="C467" s="32"/>
@@ -11384,7 +11780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="468" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A468" s="30"/>
       <c r="B468" s="12"/>
       <c r="C468" s="32"/>
@@ -11400,7 +11796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="469" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A469" s="30"/>
       <c r="B469" s="12"/>
       <c r="C469" s="32"/>
@@ -11416,7 +11812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="470" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A470" s="30"/>
       <c r="B470" s="12"/>
       <c r="C470" s="32"/>
@@ -11432,7 +11828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="471" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A471" s="30"/>
       <c r="B471" s="12"/>
       <c r="C471" s="32"/>
@@ -11448,7 +11844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="472" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A472" s="30"/>
       <c r="B472" s="12"/>
       <c r="C472" s="32"/>
@@ -11464,7 +11860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="473" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A473" s="30"/>
       <c r="B473" s="12"/>
       <c r="C473" s="32"/>
@@ -11480,7 +11876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="474" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A474" s="30"/>
       <c r="B474" s="12"/>
       <c r="C474" s="32"/>
@@ -11496,7 +11892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="475" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A475" s="30"/>
       <c r="B475" s="12"/>
       <c r="C475" s="32"/>
@@ -11512,7 +11908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="476" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A476" s="30"/>
       <c r="B476" s="12"/>
       <c r="C476" s="32"/>
@@ -11528,7 +11924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="477" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A477" s="30"/>
       <c r="B477" s="12"/>
       <c r="C477" s="32"/>
@@ -11544,7 +11940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="478" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A478" s="30"/>
       <c r="B478" s="12"/>
       <c r="C478" s="32"/>
@@ -11560,7 +11956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="479" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A479" s="30"/>
       <c r="B479" s="12"/>
       <c r="C479" s="32"/>
@@ -11576,7 +11972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="480" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A480" s="30"/>
       <c r="B480" s="12"/>
       <c r="C480" s="32"/>
@@ -11592,7 +11988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="481" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A481" s="30"/>
       <c r="B481" s="12"/>
       <c r="C481" s="32"/>
@@ -11608,7 +12004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="482" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A482" s="30"/>
       <c r="B482" s="12"/>
       <c r="C482" s="32"/>
@@ -11624,7 +12020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="483" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A483" s="30"/>
       <c r="B483" s="12"/>
       <c r="C483" s="32"/>
@@ -11640,7 +12036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="484" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A484" s="30"/>
       <c r="B484" s="12"/>
       <c r="C484" s="32"/>
@@ -11656,7 +12052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="485" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A485" s="30"/>
       <c r="B485" s="12"/>
       <c r="C485" s="32"/>
@@ -11672,7 +12068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="486" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A486" s="30"/>
       <c r="B486" s="12"/>
       <c r="C486" s="32"/>
@@ -11688,7 +12084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="487" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A487" s="30"/>
       <c r="B487" s="12"/>
       <c r="C487" s="32"/>
@@ -11704,7 +12100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="488" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A488" s="30"/>
       <c r="B488" s="12"/>
       <c r="C488" s="32"/>
@@ -11720,7 +12116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="489" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A489" s="30"/>
       <c r="B489" s="12"/>
       <c r="C489" s="32"/>
@@ -11736,7 +12132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="490" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A490" s="30"/>
       <c r="B490" s="31"/>
       <c r="C490" s="32"/>
@@ -11752,7 +12148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="491" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A491" s="30"/>
       <c r="B491" s="31"/>
       <c r="C491" s="32"/>
@@ -11768,7 +12164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="492" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A492" s="30"/>
       <c r="B492" s="31"/>
       <c r="C492" s="32"/>
@@ -11784,7 +12180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="493" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A493" s="30"/>
       <c r="B493" s="31"/>
       <c r="C493" s="32"/>
@@ -11800,7 +12196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="494" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A494" s="30"/>
       <c r="B494" s="31"/>
       <c r="C494" s="32"/>
@@ -11816,7 +12212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="495" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A495" s="30"/>
       <c r="B495" s="31"/>
       <c r="C495" s="32"/>
@@ -11832,7 +12228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="496" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A496" s="30"/>
       <c r="B496" s="31"/>
       <c r="C496" s="32"/>
@@ -11848,7 +12244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="497" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A497" s="30"/>
       <c r="B497" s="31"/>
       <c r="C497" s="32"/>
@@ -11864,7 +12260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="498" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A498" s="30"/>
       <c r="B498" s="31"/>
       <c r="C498" s="32"/>
@@ -11880,7 +12276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="499" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A499" s="30"/>
       <c r="B499" s="31"/>
       <c r="C499" s="32"/>
@@ -11896,7 +12292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="500" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A500" s="30"/>
       <c r="B500" s="31"/>
       <c r="C500" s="32"/>
@@ -11912,7 +12308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="501" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A501" s="30"/>
       <c r="B501" s="31"/>
       <c r="C501" s="32"/>
@@ -11928,7 +12324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="502" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A502" s="30"/>
       <c r="B502" s="31"/>
       <c r="C502" s="32"/>
@@ -11944,7 +12340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="503" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A503" s="30"/>
       <c r="B503" s="31"/>
       <c r="C503" s="32"/>
@@ -11960,7 +12356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="504" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A504" s="30"/>
       <c r="B504" s="31"/>
       <c r="C504" s="32"/>
@@ -11976,7 +12372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="505" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A505" s="30"/>
       <c r="B505" s="31"/>
       <c r="C505" s="32"/>
@@ -11992,7 +12388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="506" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A506" s="30"/>
       <c r="B506" s="31"/>
       <c r="C506" s="32"/>
@@ -12008,7 +12404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="507" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A507" s="30"/>
       <c r="B507" s="31"/>
       <c r="C507" s="32"/>
@@ -12024,7 +12420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="508" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A508" s="30"/>
       <c r="B508" s="31"/>
       <c r="C508" s="32"/>
@@ -12040,7 +12436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="509" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A509" s="30"/>
       <c r="B509" s="31"/>
       <c r="C509" s="32"/>
@@ -12056,7 +12452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="510" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A510" s="30"/>
       <c r="B510" s="31"/>
       <c r="C510" s="32"/>
@@ -12072,7 +12468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="511" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A511" s="30"/>
       <c r="B511" s="31"/>
       <c r="C511" s="32"/>
@@ -12088,7 +12484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="512" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A512" s="30"/>
       <c r="B512" s="31"/>
       <c r="C512" s="32"/>
@@ -12104,7 +12500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="513" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A513" s="30"/>
       <c r="B513" s="31"/>
       <c r="C513" s="32"/>
@@ -12120,7 +12516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="514" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A514" s="30"/>
       <c r="B514" s="31"/>
       <c r="C514" s="32"/>
@@ -12136,7 +12532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="515" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A515" s="30"/>
       <c r="B515" s="31"/>
       <c r="C515" s="32"/>
@@ -12152,7 +12548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="516" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A516" s="30"/>
       <c r="B516" s="31"/>
       <c r="C516" s="32"/>
@@ -12168,7 +12564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="517" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A517" s="30"/>
       <c r="B517" s="31"/>
       <c r="C517" s="32"/>
@@ -12184,7 +12580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="518" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A518" s="30"/>
       <c r="B518" s="31"/>
       <c r="C518" s="32"/>
@@ -12200,7 +12596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="519" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A519" s="30"/>
       <c r="B519" s="31"/>
       <c r="C519" s="32"/>
@@ -12216,7 +12612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="520" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A520" s="30"/>
       <c r="B520" s="31"/>
       <c r="C520" s="32"/>
@@ -12232,7 +12628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="521" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A521" s="30"/>
       <c r="B521" s="31"/>
       <c r="C521" s="32"/>
@@ -12248,7 +12644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="522" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A522" s="30"/>
       <c r="B522" s="31"/>
       <c r="C522" s="32"/>
@@ -12264,7 +12660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="523" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A523" s="30"/>
       <c r="B523" s="31"/>
       <c r="C523" s="32"/>
@@ -12280,7 +12676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="524" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A524" s="30"/>
       <c r="B524" s="31"/>
       <c r="C524" s="32"/>
@@ -12296,7 +12692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="525" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A525" s="30"/>
       <c r="B525" s="31"/>
       <c r="C525" s="32"/>
@@ -12312,7 +12708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="526" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A526" s="30"/>
       <c r="B526" s="31"/>
       <c r="C526" s="32"/>
@@ -12328,7 +12724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="527" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A527" s="30"/>
       <c r="B527" s="31"/>
       <c r="C527" s="32"/>
@@ -12344,7 +12740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="528" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A528" s="30"/>
       <c r="B528" s="31"/>
       <c r="C528" s="32"/>
@@ -12360,7 +12756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="529" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A529" s="30"/>
       <c r="B529" s="31"/>
       <c r="C529" s="32"/>
@@ -12376,7 +12772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="530" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A530" s="30"/>
       <c r="B530" s="31"/>
       <c r="C530" s="32"/>
@@ -12392,7 +12788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="531" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A531" s="30"/>
       <c r="B531" s="31"/>
       <c r="C531" s="32"/>
@@ -12408,7 +12804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="532" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A532" s="30"/>
       <c r="B532" s="31"/>
       <c r="C532" s="32"/>
@@ -12424,7 +12820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="533" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A533" s="30"/>
       <c r="B533" s="31"/>
       <c r="C533" s="32"/>
@@ -12440,7 +12836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="534" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A534" s="30"/>
       <c r="B534" s="31"/>
       <c r="C534" s="32"/>
@@ -12456,7 +12852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="535" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A535" s="30"/>
       <c r="B535" s="31"/>
       <c r="C535" s="32"/>
@@ -12472,7 +12868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="536" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A536" s="30"/>
       <c r="B536" s="31"/>
       <c r="C536" s="32"/>
@@ -12488,7 +12884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="537" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A537" s="30"/>
       <c r="B537" s="31"/>
       <c r="C537" s="32"/>
@@ -12504,7 +12900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="538" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A538" s="30"/>
       <c r="B538" s="31"/>
       <c r="C538" s="32"/>
@@ -12520,7 +12916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="539" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A539" s="30"/>
       <c r="B539" s="31"/>
       <c r="C539" s="32"/>
@@ -12536,7 +12932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="540" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A540" s="30"/>
       <c r="B540" s="31"/>
       <c r="C540" s="32"/>
@@ -12552,7 +12948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="541" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A541" s="30"/>
       <c r="B541" s="31"/>
       <c r="C541" s="32"/>
@@ -12568,7 +12964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="542" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A542" s="30"/>
       <c r="B542" s="31"/>
       <c r="C542" s="32"/>
@@ -12584,7 +12980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="543" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A543" s="30"/>
       <c r="B543" s="31"/>
       <c r="C543" s="32"/>
@@ -12600,7 +12996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="544" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A544" s="30"/>
       <c r="B544" s="31"/>
       <c r="C544" s="32"/>
@@ -12616,7 +13012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="545" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A545" s="30"/>
       <c r="B545" s="31"/>
       <c r="C545" s="32"/>
@@ -12632,7 +13028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="546" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A546" s="30"/>
       <c r="B546" s="31"/>
       <c r="C546" s="32"/>
@@ -12648,7 +13044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="547" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A547" s="30"/>
       <c r="B547" s="31"/>
       <c r="C547" s="32"/>
@@ -12664,7 +13060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="548" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A548" s="30"/>
       <c r="B548" s="31"/>
       <c r="C548" s="32"/>
@@ -12680,7 +13076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="549" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A549" s="30"/>
       <c r="B549" s="31"/>
       <c r="C549" s="32"/>
@@ -12696,7 +13092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="550" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A550" s="30"/>
       <c r="B550" s="31"/>
       <c r="C550" s="32"/>
@@ -12712,7 +13108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="551" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A551" s="30"/>
       <c r="B551" s="31"/>
       <c r="C551" s="32"/>
@@ -12728,7 +13124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="552" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A552" s="30"/>
       <c r="B552" s="31"/>
       <c r="C552" s="32"/>
@@ -12744,7 +13140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="553" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A553" s="30"/>
       <c r="B553" s="31"/>
       <c r="C553" s="32"/>
@@ -12760,7 +13156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="554" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A554" s="30"/>
       <c r="B554" s="31"/>
       <c r="C554" s="32"/>
@@ -12776,7 +13172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="555" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A555" s="30"/>
       <c r="B555" s="31"/>
       <c r="C555" s="32"/>
@@ -12792,7 +13188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="556" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A556" s="30"/>
       <c r="B556" s="31"/>
       <c r="C556" s="32"/>
@@ -12808,7 +13204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="557" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A557" s="30"/>
       <c r="B557" s="31"/>
       <c r="C557" s="32"/>
@@ -12824,7 +13220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="558" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A558" s="30"/>
       <c r="B558" s="31"/>
       <c r="C558" s="32"/>
@@ -12840,7 +13236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="559" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A559" s="30"/>
       <c r="B559" s="31"/>
       <c r="C559" s="32"/>
@@ -12856,7 +13252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="560" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A560" s="30"/>
       <c r="B560" s="31"/>
       <c r="C560" s="32"/>
@@ -12872,7 +13268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="561" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A561" s="30"/>
       <c r="B561" s="31"/>
       <c r="C561" s="32"/>
@@ -12888,7 +13284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="562" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A562" s="30"/>
       <c r="B562" s="31"/>
       <c r="C562" s="32"/>
@@ -12904,7 +13300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="563" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A563" s="30"/>
       <c r="B563" s="31"/>
       <c r="C563" s="32"/>
@@ -12920,7 +13316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="564" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A564" s="30"/>
       <c r="B564" s="31"/>
       <c r="C564" s="32"/>
@@ -12936,7 +13332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="565" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A565" s="30"/>
       <c r="B565" s="31"/>
       <c r="C565" s="32"/>
@@ -12952,7 +13348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="566" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A566" s="30"/>
       <c r="B566" s="31"/>
       <c r="C566" s="32"/>
@@ -12968,7 +13364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="567" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A567" s="30"/>
       <c r="B567" s="31"/>
       <c r="C567" s="32"/>
@@ -12984,7 +13380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="568" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A568" s="30"/>
       <c r="B568" s="31"/>
       <c r="C568" s="32"/>
@@ -13000,7 +13396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="569" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A569" s="30"/>
       <c r="B569" s="31"/>
       <c r="C569" s="32"/>
@@ -13016,7 +13412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="570" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A570" s="30"/>
       <c r="B570" s="31"/>
       <c r="C570" s="32"/>
@@ -13032,7 +13428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="571" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A571" s="30"/>
       <c r="B571" s="31"/>
       <c r="C571" s="32"/>
@@ -13048,7 +13444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="572" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A572" s="30"/>
       <c r="B572" s="31"/>
       <c r="C572" s="32"/>
@@ -13064,7 +13460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="573" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A573" s="30"/>
       <c r="B573" s="31"/>
       <c r="C573" s="32"/>
@@ -13080,7 +13476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="574" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A574" s="30"/>
       <c r="B574" s="31"/>
       <c r="C574" s="32"/>
@@ -13096,7 +13492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="575" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A575" s="30"/>
       <c r="B575" s="31"/>
       <c r="C575" s="32"/>
@@ -13112,7 +13508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="576" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A576" s="30"/>
       <c r="B576" s="31"/>
       <c r="C576" s="32"/>
@@ -13128,7 +13524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="577" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A577" s="30"/>
       <c r="B577" s="31"/>
       <c r="C577" s="32"/>
@@ -13144,7 +13540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="578" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A578" s="30"/>
       <c r="B578" s="31"/>
       <c r="C578" s="32"/>
@@ -13160,7 +13556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="579" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A579" s="30"/>
       <c r="B579" s="31"/>
       <c r="C579" s="32"/>
@@ -13176,7 +13572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="580" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A580" s="30"/>
       <c r="B580" s="31"/>
       <c r="C580" s="32"/>
@@ -13192,7 +13588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="581" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A581" s="30"/>
       <c r="B581" s="31"/>
       <c r="C581" s="32"/>
@@ -13208,7 +13604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="582" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A582" s="30"/>
       <c r="B582" s="31"/>
       <c r="C582" s="32"/>
@@ -13224,7 +13620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="583" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A583" s="30"/>
       <c r="B583" s="31"/>
       <c r="C583" s="32"/>
@@ -13240,7 +13636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="584" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A584" s="35"/>
       <c r="B584" s="31"/>
       <c r="C584" s="32"/>
@@ -13256,7 +13652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="585" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A585" s="36"/>
       <c r="B585" s="13"/>
       <c r="C585" s="8"/>
@@ -13272,27 +13668,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="586" spans="1:11" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
-    <row r="587" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="587" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D587" s="37"/>
       <c r="E587" s="37"/>
     </row>
-    <row r="588" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D588" s="37"/>
       <c r="E588" s="37"/>
       <c r="G588" s="29"/>
     </row>
-    <row r="589" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D589" s="37"/>
       <c r="E589" s="37"/>
       <c r="G589" s="29"/>
     </row>
-    <row r="590" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D590" s="37"/>
       <c r="E590" s="37"/>
       <c r="G590" s="29"/>
     </row>
-    <row r="591" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D591" s="37"/>
       <c r="E591" s="37"/>
       <c r="G591" s="29"/>
